--- a/data/Type3_conflicts.xlsx
+++ b/data/Type3_conflicts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schien/Documents/GitHub/achiasmy-synthesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54E8CDD8-437B-C648-8FAD-AFB770188415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B802BBA1-A427-DC46-9AE1-197D0E49ED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="34300" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3849,90 +3849,90 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="A35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G35" t="s">
-        <v>33</v>
-      </c>
-      <c r="H35" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="G35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L35" t="s">
+      <c r="K35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="A36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G36" t="s">
-        <v>33</v>
-      </c>
-      <c r="H36" t="s">
-        <v>26</v>
-      </c>
-      <c r="I36" t="s">
+      <c r="G36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K36" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="K36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M36" t="s">
+      <c r="M36" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="2">
         <v>15</v>
       </c>
     </row>
@@ -4553,90 +4553,90 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" t="s">
-        <v>94</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="A51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G51" t="s">
-        <v>33</v>
-      </c>
-      <c r="H51" t="s">
-        <v>26</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="G51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J51" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K51" t="s">
-        <v>27</v>
-      </c>
-      <c r="L51" t="s">
+      <c r="K51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L51" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M51" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="N51">
+      <c r="N51" s="2">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" t="s">
-        <v>94</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="A52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G52" t="s">
-        <v>33</v>
-      </c>
-      <c r="H52" t="s">
-        <v>26</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="G52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J52" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K52" t="s">
-        <v>27</v>
-      </c>
-      <c r="L52" t="s">
+      <c r="K52" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M52" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="2">
         <v>22</v>
       </c>
     </row>
@@ -5301,90 +5301,90 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>14</v>
-      </c>
-      <c r="B68" t="s">
-        <v>93</v>
-      </c>
-      <c r="C68" t="s">
-        <v>94</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="A68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G68" t="s">
-        <v>33</v>
-      </c>
-      <c r="H68" t="s">
-        <v>26</v>
-      </c>
-      <c r="I68" t="s">
+      <c r="G68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I68" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K68" t="s">
-        <v>27</v>
-      </c>
-      <c r="L68" t="s">
+      <c r="K68" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="M68" t="s">
+      <c r="M68" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>14</v>
-      </c>
-      <c r="B69" t="s">
-        <v>93</v>
-      </c>
-      <c r="C69" t="s">
-        <v>94</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="A69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G69" t="s">
-        <v>33</v>
-      </c>
-      <c r="H69" t="s">
-        <v>26</v>
-      </c>
-      <c r="I69" t="s">
+      <c r="G69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="J69" t="s">
+      <c r="J69" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K69" t="s">
-        <v>27</v>
-      </c>
-      <c r="L69" t="s">
+      <c r="K69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="M69" t="s">
+      <c r="M69" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="N69">
+      <c r="N69" s="2">
         <v>30</v>
       </c>
     </row>
@@ -6489,90 +6489,90 @@
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>14</v>
-      </c>
-      <c r="B95" t="s">
-        <v>93</v>
-      </c>
-      <c r="C95" t="s">
-        <v>94</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="A95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G95" t="s">
-        <v>33</v>
-      </c>
-      <c r="H95" t="s">
-        <v>26</v>
-      </c>
-      <c r="I95" t="s">
+      <c r="G95" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J95" t="s">
+      <c r="J95" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K95" t="s">
-        <v>27</v>
-      </c>
-      <c r="L95" t="s">
+      <c r="K95" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L95" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="M95" t="s">
+      <c r="M95" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="N95">
+      <c r="N95" s="2">
         <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>14</v>
-      </c>
-      <c r="B96" t="s">
-        <v>93</v>
-      </c>
-      <c r="C96" t="s">
-        <v>94</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="A96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F96" t="s">
+      <c r="F96" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G96" t="s">
-        <v>33</v>
-      </c>
-      <c r="H96" t="s">
-        <v>26</v>
-      </c>
-      <c r="I96" t="s">
+      <c r="G96" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I96" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J96" t="s">
+      <c r="J96" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K96" t="s">
-        <v>27</v>
-      </c>
-      <c r="L96" t="s">
+      <c r="K96" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L96" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="M96" t="s">
+      <c r="M96" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="N96">
+      <c r="N96" s="2">
         <v>43</v>
       </c>
     </row>

--- a/data/Type3_conflicts.xlsx
+++ b/data/Type3_conflicts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schien/Documents/GitHub/achiasmy-synthesis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B802BBA1-A427-DC46-9AE1-197D0E49ED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C435333-4320-FE43-A3AA-E9A30182C417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="34300" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2147,7 +2147,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2159,6 +2159,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2190,12 +2197,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2993,7 +3001,7 @@
       <c r="F12" t="s">
         <v>68</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="H12" t="s">
@@ -3028,7 +3036,7 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="3" t="s">
         <v>44</v>
       </c>
       <c r="H13" t="s">
@@ -3961,7 +3969,7 @@
       <c r="H37" t="s">
         <v>26</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J37" t="s">
@@ -4005,7 +4013,7 @@
       <c r="H38" t="s">
         <v>26</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="3" t="s">
         <v>113</v>
       </c>
       <c r="J38" t="s">
@@ -4049,7 +4057,7 @@
       <c r="H39" t="s">
         <v>26</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J39" t="s">
@@ -4093,7 +4101,7 @@
       <c r="H40" t="s">
         <v>26</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="3" t="s">
         <v>115</v>
       </c>
       <c r="J40" t="s">
@@ -4137,7 +4145,7 @@
       <c r="H41" t="s">
         <v>26</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="3" t="s">
         <v>115</v>
       </c>
       <c r="J41" t="s">
@@ -4181,7 +4189,7 @@
       <c r="H42" t="s">
         <v>26</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="3" t="s">
         <v>121</v>
       </c>
       <c r="J42" t="s">
@@ -4225,7 +4233,7 @@
       <c r="H43" t="s">
         <v>26</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="3" t="s">
         <v>37</v>
       </c>
       <c r="J43" t="s">
@@ -4269,7 +4277,7 @@
       <c r="H44" t="s">
         <v>26</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="3" t="s">
         <v>62</v>
       </c>
       <c r="J44" t="s">
@@ -4313,7 +4321,7 @@
       <c r="H45" t="s">
         <v>26</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="3" t="s">
         <v>45</v>
       </c>
       <c r="J45" t="s">
@@ -4357,7 +4365,7 @@
       <c r="H46" t="s">
         <v>26</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J46" t="s">
@@ -4401,7 +4409,7 @@
       <c r="H47" t="s">
         <v>26</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="J47" t="s">
@@ -4445,7 +4453,7 @@
       <c r="H48" t="s">
         <v>26</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="3" t="s">
         <v>134</v>
       </c>
       <c r="J48" t="s">
@@ -4489,7 +4497,7 @@
       <c r="H49" t="s">
         <v>26</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J49" t="s">
@@ -4533,7 +4541,7 @@
       <c r="H50" t="s">
         <v>26</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="J50" t="s">
@@ -4665,13 +4673,13 @@
       <c r="H53" t="s">
         <v>26</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I53" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J53" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K53" t="s">
+      <c r="K53" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L53" t="s">
@@ -4709,13 +4717,13 @@
       <c r="H54" t="s">
         <v>26</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I54" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J54" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K54" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L54" t="s">
@@ -4753,13 +4761,13 @@
       <c r="H55" t="s">
         <v>26</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J55" t="s">
+      <c r="J55" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K55" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L55" t="s">
@@ -4797,13 +4805,13 @@
       <c r="H56" t="s">
         <v>26</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J56" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K56" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L56" t="s">
@@ -4841,13 +4849,13 @@
       <c r="H57" t="s">
         <v>26</v>
       </c>
-      <c r="I57" t="s">
+      <c r="I57" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J57" t="s">
+      <c r="J57" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K57" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L57" t="s">
@@ -4885,7 +4893,7 @@
       <c r="H58" t="s">
         <v>26</v>
       </c>
-      <c r="I58" t="s">
+      <c r="I58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="J58" t="s">
@@ -4929,7 +4937,7 @@
       <c r="H59" t="s">
         <v>26</v>
       </c>
-      <c r="I59" t="s">
+      <c r="I59" s="3" t="s">
         <v>144</v>
       </c>
       <c r="J59" t="s">
@@ -4973,7 +4981,7 @@
       <c r="H60" t="s">
         <v>26</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I60" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J60" t="s">
@@ -5017,7 +5025,7 @@
       <c r="H61" t="s">
         <v>26</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I61" s="3" t="s">
         <v>45</v>
       </c>
       <c r="J61" t="s">
@@ -5064,7 +5072,7 @@
       <c r="I62" t="s">
         <v>52</v>
       </c>
-      <c r="J62" t="s">
+      <c r="J62" s="3" t="s">
         <v>98</v>
       </c>
       <c r="K62" t="s">
@@ -5108,7 +5116,7 @@
       <c r="I63" t="s">
         <v>52</v>
       </c>
-      <c r="J63" t="s">
+      <c r="J63" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K63" t="s">
@@ -5149,7 +5157,7 @@
       <c r="H64" t="s">
         <v>26</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I64" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J64" t="s">
@@ -5193,7 +5201,7 @@
       <c r="H65" t="s">
         <v>26</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I65" s="3" t="s">
         <v>167</v>
       </c>
       <c r="J65" t="s">
@@ -5240,7 +5248,7 @@
       <c r="I66" t="s">
         <v>52</v>
       </c>
-      <c r="J66" t="s">
+      <c r="J66" s="3" t="s">
         <v>98</v>
       </c>
       <c r="K66" t="s">
@@ -5284,7 +5292,7 @@
       <c r="I67" t="s">
         <v>52</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="3" t="s">
         <v>105</v>
       </c>
       <c r="K67" t="s">
@@ -5413,7 +5421,7 @@
       <c r="H70" t="s">
         <v>26</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I70" s="3" t="s">
         <v>37</v>
       </c>
       <c r="J70" t="s">
@@ -5457,7 +5465,7 @@
       <c r="H71" t="s">
         <v>26</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J71" t="s">
@@ -5501,7 +5509,7 @@
       <c r="H72" t="s">
         <v>26</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I72" s="3" t="s">
         <v>144</v>
       </c>
       <c r="J72" t="s">
@@ -5545,7 +5553,7 @@
       <c r="H73" t="s">
         <v>26</v>
       </c>
-      <c r="I73" t="s">
+      <c r="I73" s="3" t="s">
         <v>180</v>
       </c>
       <c r="J73" t="s">
@@ -5592,10 +5600,10 @@
       <c r="I74" t="s">
         <v>114</v>
       </c>
-      <c r="J74" t="s">
+      <c r="J74" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="K74" t="s">
+      <c r="K74" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L74" t="s">
@@ -5636,10 +5644,10 @@
       <c r="I75" t="s">
         <v>114</v>
       </c>
-      <c r="J75" t="s">
+      <c r="J75" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K75" t="s">
+      <c r="K75" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L75" t="s">
@@ -5768,10 +5776,10 @@
       <c r="I78" t="s">
         <v>45</v>
       </c>
-      <c r="J78" t="s">
+      <c r="J78" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K78" t="s">
+      <c r="K78" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L78" t="s">
@@ -5812,10 +5820,10 @@
       <c r="I79" t="s">
         <v>45</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J79" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K79" t="s">
+      <c r="K79" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L79" t="s">
@@ -5856,10 +5864,10 @@
       <c r="I80" t="s">
         <v>45</v>
       </c>
-      <c r="J80" t="s">
+      <c r="J80" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K80" t="s">
+      <c r="K80" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L80" t="s">
@@ -5900,10 +5908,10 @@
       <c r="I81" t="s">
         <v>45</v>
       </c>
-      <c r="J81" t="s">
+      <c r="J81" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K81" t="s">
+      <c r="K81" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L81" t="s">
@@ -5941,7 +5949,7 @@
       <c r="H82" t="s">
         <v>26</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I82" s="3" t="s">
         <v>62</v>
       </c>
       <c r="J82" t="s">
@@ -5985,7 +5993,7 @@
       <c r="H83" t="s">
         <v>26</v>
       </c>
-      <c r="I83" t="s">
+      <c r="I83" s="3" t="s">
         <v>172</v>
       </c>
       <c r="J83" t="s">
@@ -6032,10 +6040,10 @@
       <c r="I84" t="s">
         <v>114</v>
       </c>
-      <c r="J84" t="s">
+      <c r="J84" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="K84" t="s">
+      <c r="K84" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L84" t="s">
@@ -6076,10 +6084,10 @@
       <c r="I85" t="s">
         <v>114</v>
       </c>
-      <c r="J85" t="s">
+      <c r="J85" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="K85" t="s">
+      <c r="K85" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L85" t="s">
@@ -6120,10 +6128,10 @@
       <c r="I86" t="s">
         <v>172</v>
       </c>
-      <c r="J86" t="s">
+      <c r="J86" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="K86" t="s">
+      <c r="K86" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L86" t="s">
@@ -6164,10 +6172,10 @@
       <c r="I87" t="s">
         <v>172</v>
       </c>
-      <c r="J87" t="s">
+      <c r="J87" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="K87" t="s">
+      <c r="K87" s="3" t="s">
         <v>27</v>
       </c>
       <c r="L87" t="s">
@@ -6208,10 +6216,10 @@
       <c r="I88" t="s">
         <v>172</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J88" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="K88" t="s">
+      <c r="K88" s="3" t="s">
         <v>47</v>
       </c>
       <c r="L88" t="s">
@@ -6252,7 +6260,7 @@
       <c r="I89" t="s">
         <v>172</v>
       </c>
-      <c r="J89" t="s">
+      <c r="J89" s="3" t="s">
         <v>98</v>
       </c>
       <c r="K89" t="s">
@@ -6296,7 +6304,7 @@
       <c r="I90" t="s">
         <v>172</v>
       </c>
-      <c r="J90" t="s">
+      <c r="J90" s="3" t="s">
         <v>203</v>
       </c>
       <c r="K90" t="s">
@@ -6337,7 +6345,7 @@
       <c r="H91" t="s">
         <v>26</v>
       </c>
-      <c r="I91" t="s">
+      <c r="I91" s="3" t="s">
         <v>134</v>
       </c>
       <c r="J91" t="s">
@@ -6381,7 +6389,7 @@
       <c r="H92" t="s">
         <v>26</v>
       </c>
-      <c r="I92" t="s">
+      <c r="I92" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J92" t="s">
@@ -6425,7 +6433,7 @@
       <c r="H93" t="s">
         <v>26</v>
       </c>
-      <c r="I93" t="s">
+      <c r="I93" s="3" t="s">
         <v>134</v>
       </c>
       <c r="J93" t="s">
@@ -6469,7 +6477,7 @@
       <c r="H94" t="s">
         <v>26</v>
       </c>
-      <c r="I94" t="s">
+      <c r="I94" s="3" t="s">
         <v>111</v>
       </c>
       <c r="J94" t="s">
